--- a/public/modele-import-participants.xlsx
+++ b/public/modele-import-participants.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participants" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Participants" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Participants'!$A$1:$F$1</definedName>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -448,6 +448,9 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -479,6 +482,104 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Statut</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Paiement</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Montant</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Moyen de paiement</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Amira Ben Salem</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>amira@example.tn</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Entreprise Exemple</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Participant</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>IE-0001</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>À accueillir</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Non payé</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mehdi Trabelsi</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mehdi@example.tn</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Entreprise Exemple</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>IE-0002</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>À accueillir</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Payé</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Espèces</t>
         </is>
       </c>
     </row>
@@ -494,7 +595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="105" customWidth="1" min="1" max="1"/>
@@ -535,6 +636,13 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Colonnes de paiement (facultatives) : « Paiement » (Payé / Non payé / Exonéré), « Montant » et « Moyen de paiement » (Espèces, Carte bancaire, Virement, Chèque, Paiement mobile).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
